--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260623.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260623.xlsx
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>79,446,748</t>
+          <t>46,423,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>46,423,000</t>
+          <t>79,446,748</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
